--- a/artfynd/A 34624-2022 artfynd.xlsx
+++ b/artfynd/A 34624-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34624-2022 artfynd.xlsx
+++ b/artfynd/A 34624-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>16817303</v>
       </c>
       <c r="B2" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581626.9874201264</v>
+        <v>581627</v>
       </c>
       <c r="R2" t="n">
-        <v>6377815.121357966</v>
+        <v>6377815</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2014-06-06</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,57 +776,60 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>16817542</v>
+        <v>103557520</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tribbhult, Sm</t>
+          <t>Österhult A34624, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581805.1117549874</v>
+        <v>581798</v>
       </c>
       <c r="R3" t="n">
-        <v>6377812.795630954</v>
+        <v>6377758</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +853,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,55 +867,51 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rebecka Le Moine</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rebecka Le Moine</t>
+          <t>Gunilla Nilsson, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>16817534</v>
+        <v>103557635</v>
       </c>
       <c r="B4" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>2180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -945,19 +919,27 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tribbhult, Sm</t>
+          <t>Österhult A34624, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581861.2140710166</v>
+        <v>581761</v>
       </c>
       <c r="R4" t="n">
-        <v>6378019.037473202</v>
+        <v>6378095</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -981,22 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-06-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-09-09</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,18 +977,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rebecka Le Moine</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rebecka Le Moine</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1026,12 +999,7 @@
         <v>103557653</v>
       </c>
       <c r="B5" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1075,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>581823.0526507967</v>
+        <v>581823</v>
       </c>
       <c r="R5" t="n">
-        <v>6378044.041638278</v>
+        <v>6378044</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1108,19 +1076,9 @@
           <t>2022-09-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,55 +1106,46 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>103557809</v>
+        <v>103557858</v>
       </c>
       <c r="B6" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>avledningsbeteende</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1204,13 +1153,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>581777.5122439554</v>
+        <v>581821</v>
       </c>
       <c r="R6" t="n">
-        <v>6378088.226695881</v>
+        <v>6378057</v>
       </c>
       <c r="S6" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1237,27 +1186,18 @@
           <t>2022-09-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-09-14</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1276,15 +1216,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>103557377</v>
+        <v>103675723</v>
       </c>
       <c r="B7" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1292,31 +1227,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -1324,17 +1259,17 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Österhult A34624, Sm</t>
+          <t>Österhult A 34624, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>581731.1694854685</v>
+        <v>582035</v>
       </c>
       <c r="R7" t="n">
-        <v>6377771.036306072</v>
+        <v>6378010</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,22 +1293,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,73 +1319,64 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Ingvor Kasselstrand, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>103557736</v>
+        <v>103684888</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Österhult A 34624, Sm</t>
+          <t>Österhult_A34624, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>581881.6350773245</v>
+        <v>581659</v>
       </c>
       <c r="R8" t="n">
-        <v>6378046.832144223</v>
+        <v>6377908</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1487,22 +1403,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1518,27 +1424,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Ingvor Kasselstrand, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>103557858</v>
+        <v>103684920</v>
       </c>
       <c r="B9" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1565,7 +1466,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1582,10 +1483,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>581821.7178487469</v>
+        <v>581843</v>
       </c>
       <c r="R9" t="n">
-        <v>6378056.900983235</v>
+        <v>6378041</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1612,22 +1513,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1655,51 +1546,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>103558109</v>
+        <v>103684942</v>
       </c>
       <c r="B10" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>avledningsbeteende</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1707,13 +1593,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>581708.4944546188</v>
+        <v>582036</v>
       </c>
       <c r="R10" t="n">
-        <v>6377801.724121038</v>
+        <v>6378042</v>
       </c>
       <c r="S10" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1735,29 +1621,14 @@
           <t>Hjorted</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>7D32084A-0D74-4D15-92F9-4A9B3A950283</t>
-        </is>
-      </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1766,6 +1637,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1780,74 +1652,61 @@
           <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>Skyddsvärda träd</t>
-        </is>
-      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103557717</v>
+        <v>103684964</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2180</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Österhult A34624, Sm</t>
+          <t>Österhult_A34624, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>581872.9770102528</v>
+        <v>581778</v>
       </c>
       <c r="R11" t="n">
-        <v>6378049.34236719</v>
+        <v>6378165</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1874,22 +1733,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1905,27 +1754,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103557635</v>
+        <v>103684990</v>
       </c>
       <c r="B12" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1965,14 +1809,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Österhult A34624, Sm</t>
+          <t>Österhult_A34624, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>581761.2287410529</v>
+        <v>582037</v>
       </c>
       <c r="R12" t="n">
-        <v>6378095.41598568</v>
+        <v>6378023</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1999,22 +1843,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2030,27 +1864,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>103557751</v>
+        <v>16817542</v>
       </c>
       <c r="B13" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2080,26 +1909,19 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Österhult_A34624, Sm</t>
+          <t>Tribbhult, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>581609.0825819599</v>
+        <v>581805</v>
       </c>
       <c r="R13" t="n">
-        <v>6378010.208891408</v>
+        <v>6377813</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2123,22 +1945,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-06-06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2022-09-14</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-09-09</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2147,84 +1959,77 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Rebecka Le Moine</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Rebecka Le Moine</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>103667325</v>
+        <v>103557751</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 34624, Österhult, Hjorted, Sm</t>
+          <t>Österhult_A34624, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>581894.9067361815</v>
+        <v>581609</v>
       </c>
       <c r="R14" t="n">
-        <v>6377948.840785887</v>
+        <v>6378011</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2248,22 +2053,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>09:30</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2279,12 +2074,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2294,12 +2089,7 @@
         <v>103667318</v>
       </c>
       <c r="B15" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2342,10 +2132,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>581875.1768653521</v>
+        <v>581875</v>
       </c>
       <c r="R15" t="n">
-        <v>6377993.545981763</v>
+        <v>6377994</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2415,37 +2205,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103675723</v>
+        <v>103675690</v>
       </c>
       <c r="B16" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2180</v>
+        <v>5442</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2455,11 +2240,10 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2467,13 +2251,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>582035.1470174128</v>
+        <v>581768</v>
       </c>
       <c r="R16" t="n">
-        <v>6378010.731694774</v>
+        <v>6378166</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2500,19 +2284,9 @@
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2533,49 +2307,44 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Ingvor Kasselstrand</t>
+          <t>Gunilla Nilsson, Magnus Kasselstrand, Ingvor Kasselstrand, Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103685451</v>
+        <v>103675701</v>
       </c>
       <c r="B17" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2587,14 +2356,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Österhult_A34624, Sm</t>
+          <t>Österhult A 34624, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>581733.4446545478</v>
+        <v>581829</v>
       </c>
       <c r="R17" t="n">
-        <v>6377845.182106871</v>
+        <v>6378134</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2624,19 +2393,9 @@
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2652,27 +2411,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson, Ingvor Kasselstrand, Larsgunnar Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103685018</v>
+        <v>103684830</v>
       </c>
       <c r="B18" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2680,35 +2434,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2716,10 +2469,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>581727.9211799297</v>
+        <v>581837</v>
       </c>
       <c r="R18" t="n">
-        <v>6377772.044919774</v>
+        <v>6377973</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2749,19 +2502,14 @@
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>40 cm diameter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2789,66 +2537,56 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>103675649</v>
+        <v>103684861</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Österhult A 34624, Sm</t>
+          <t>Österhult_A34624, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>581746.0531663223</v>
+        <v>581949</v>
       </c>
       <c r="R19" t="n">
-        <v>6378101.016852665</v>
+        <v>6377961</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2878,19 +2616,9 @@
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2906,54 +2634,49 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Ingvor Kasselstrand, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>103675701</v>
+        <v>103685451</v>
       </c>
       <c r="B20" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92567</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>6031</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2965,14 +2688,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Österhult A 34624, Sm</t>
+          <t>Österhult_A34624, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>581828.7766910834</v>
+        <v>581733</v>
       </c>
       <c r="R20" t="n">
-        <v>6378133.8226136</v>
+        <v>6377845</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3002,19 +2725,9 @@
           <t>2022-09-20</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3030,81 +2743,76 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Ingvor Kasselstrand, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>103675569</v>
+        <v>103557809</v>
       </c>
       <c r="B21" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221144</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Österhult A 34624, Sm</t>
+          <t>Österhult_A34624, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>581701.7761980852</v>
+        <v>581777</v>
       </c>
       <c r="R21" t="n">
-        <v>6377734.468835304</v>
+        <v>6378089</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3128,22 +2836,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3152,70 +2850,64 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Ingvor Kasselstrand</t>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>103684942</v>
+        <v>103558109</v>
       </c>
       <c r="B22" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2180</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>avledningsbeteende</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3223,13 +2915,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>582035.6050818597</v>
+        <v>581709</v>
       </c>
       <c r="R22" t="n">
-        <v>6378041.345961684</v>
+        <v>6377801</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3251,24 +2943,19 @@
           <t>Hjorted</t>
         </is>
       </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>7D32084A-0D74-4D15-92F9-4A9B3A950283</t>
+        </is>
+      </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3277,7 +2964,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3292,66 +2978,69 @@
           <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Skyddsvärda träd</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>103684888</v>
+        <v>103557717</v>
       </c>
       <c r="B23" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Österhult_A34624, Sm</t>
+          <t>Österhult A34624, Sm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>581659.5507969204</v>
+        <v>581873</v>
       </c>
       <c r="R23" t="n">
-        <v>6377908.130681653</v>
+        <v>6378050</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3378,22 +3067,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3409,74 +3088,73 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>103684920</v>
+        <v>103557736</v>
       </c>
       <c r="B24" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Österhult_A34624, Sm</t>
+          <t>Österhult A 34624, Sm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>581843.0142818516</v>
+        <v>581882</v>
       </c>
       <c r="R24" t="n">
-        <v>6378041.221967795</v>
+        <v>6378047</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3503,22 +3181,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3534,54 +3202,49 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson, Ingvor Kasselstrand, Larsgunnar Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>103675813</v>
+        <v>103557764</v>
       </c>
       <c r="B25" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3598,14 +3261,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Österhult A 34624, Sm</t>
+          <t>Österhult A34624, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>582042.5515904364</v>
+        <v>581879</v>
       </c>
       <c r="R25" t="n">
-        <v>6378123.635360875</v>
+        <v>6378052</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3632,22 +3295,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3668,69 +3321,68 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Larsgunnar Nilsson, Ingvor Kasselstrand</t>
+          <t>Gunilla Nilsson, Ingvor Kasselstrand, Larsgunnar Nilsson, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>103684990</v>
+        <v>103557797</v>
       </c>
       <c r="B26" t="n">
-        <v>93375</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Österhult_A34624, Sm</t>
+          <t>Österhult A34624, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>582037.0380588513</v>
+        <v>581886</v>
       </c>
       <c r="R26" t="n">
-        <v>6378023.656214488</v>
+        <v>6378054</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3757,22 +3409,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3788,62 +3430,58 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Magnus Kasselstrand, Ingvor Kasselstrand</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>103684861</v>
+        <v>103557907</v>
       </c>
       <c r="B27" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3851,10 +3489,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>581948.9828119696</v>
+        <v>581870</v>
       </c>
       <c r="R27" t="n">
-        <v>6377961.743309092</v>
+        <v>6378066</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3881,22 +3519,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3924,50 +3552,46 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>103684830</v>
+        <v>103557929</v>
       </c>
       <c r="B28" t="n">
-        <v>90008</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3975,10 +3599,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>581836.8581239132</v>
+        <v>581873</v>
       </c>
       <c r="R28" t="n">
-        <v>6377972.907721612</v>
+        <v>6378059</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -4005,27 +3629,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-09-20</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>40 cm diameter</t>
+          <t>2022-09-14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4050,6 +3659,688 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>103667325</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>A 34624, Österhult, Hjorted, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>581895</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6377949</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>103675649</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Österhult A 34624, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>581746</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6378101</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Ingvor Kasselstrand, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>103557377</v>
+      </c>
+      <c r="B31" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Österhult A34624, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>581731</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6377771</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2022-09-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Ingvor Kasselstrand, Larsgunnar Nilsson, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>103675569</v>
+      </c>
+      <c r="B32" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Österhult A 34624, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>581702</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6377735</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>103675813</v>
+      </c>
+      <c r="B33" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Österhult A 34624, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>582043</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6378123</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Gunilla Nilsson, Larsgunnar Nilsson, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>103685018</v>
+      </c>
+      <c r="B34" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Österhult_A34624, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>581728</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6377772</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-09-20</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Larsgunnar Nilsson, Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
